--- a/churches-status.xlsx
+++ b/churches-status.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gaps" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All churches'!$A$1:$I$307</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$I$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All churches'!$A$1:$I$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$I$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -560,16 +560,16 @@
         <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
@@ -593,16 +593,16 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>4</v>
@@ -626,16 +626,16 @@
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>7</v>
@@ -659,16 +659,16 @@
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>4</v>
@@ -758,16 +758,16 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -857,16 +857,16 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>23</v>
@@ -890,16 +890,16 @@
         <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>11</v>
@@ -920,29 +920,29 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
@@ -956,16 +956,16 @@
         <v>37</v>
       </c>
       <c r="C15" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>13</v>
@@ -986,25 +986,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>264</v>
+        <v>305</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>264</v>
+        <v>305</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>121</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I307"/>
+  <dimension ref="A1:I306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1656,14 +1656,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
@@ -1840,14 +1840,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
@@ -3001,14 +3001,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -3189,14 +3189,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -3467,14 +3467,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -3514,14 +3514,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -3561,14 +3561,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -4399,14 +4399,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H73" s="5" t="inlineStr">
@@ -4722,14 +4722,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H80" s="5" t="inlineStr">
@@ -5372,14 +5372,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -7314,14 +7314,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H136" s="5" t="inlineStr">
@@ -7496,14 +7496,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H140" s="5" t="inlineStr">
@@ -7731,14 +7731,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H145" s="5" t="inlineStr">
@@ -9389,14 +9389,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G181" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
@@ -9663,14 +9663,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G187" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H187" s="4" t="n">
@@ -10025,14 +10025,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F195" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G195" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H195" s="4" t="n">
@@ -10483,14 +10483,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F205" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G205" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F205" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H205" s="4" t="n">
@@ -10712,14 +10712,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F210" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G210" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H210" s="4" t="n">
@@ -10804,14 +10804,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F212" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G212" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F212" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H212" s="5" t="inlineStr">
@@ -10896,14 +10896,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G214" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F214" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H214" s="5" t="inlineStr">
@@ -10990,14 +10990,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F216" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G216" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H216" s="5" t="inlineStr">
@@ -11311,14 +11311,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F223" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G223" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H223" s="5" t="inlineStr">
@@ -11358,14 +11358,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F224" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G224" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H224" s="5" t="inlineStr">
@@ -11405,14 +11405,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F225" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G225" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H225" s="5" t="inlineStr">
@@ -11683,14 +11683,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F231" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G231" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F231" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G231" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H231" s="5" t="inlineStr">
@@ -12049,14 +12049,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F239" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G239" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F239" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G239" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H239" s="5" t="inlineStr">
@@ -12096,14 +12096,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F240" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G240" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G240" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H240" s="5" t="inlineStr">
@@ -12280,14 +12280,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F244" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G244" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F244" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G244" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H244" s="4" t="n">
@@ -12693,14 +12693,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F253" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G253" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F253" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G253" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H253" s="5" t="inlineStr">
@@ -12785,14 +12785,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F255" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G255" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F255" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H255" s="5" t="inlineStr">
@@ -12926,14 +12926,14 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F258" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G258" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F258" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G258" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H258" s="5" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Porous</t>
+          <t>Portland Cottage</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>St. Augustine's Church</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>st-augustine-s-church-porous-clarendon</t>
+          <t>st-john-s-portland-cottage-clarendon</t>
         </is>
       </c>
     </row>
@@ -13002,12 +13002,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Portland Cottage</t>
+          <t>Race Course</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>St. Thomas'</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>st-john-s-portland-cottage-clarendon</t>
+          <t>st-thomas-race-course-clarendon</t>
         </is>
       </c>
     </row>
@@ -13049,12 +13049,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Race Course</t>
+          <t>Red Hills (Clarendon)</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>St. Thomas'</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>st-thomas-race-course-clarendon</t>
+          <t>st-george-s-red-hills-clarendon</t>
         </is>
       </c>
     </row>
@@ -13096,12 +13096,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Red Hills (Clarendon)</t>
+          <t>Rhoden Hall</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>St. Peter's</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>st-george-s-red-hills-clarendon</t>
+          <t>st-peter-s-rhoden-hall-clarendon</t>
         </is>
       </c>
     </row>
@@ -13143,12 +13143,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Rhoden Hall</t>
+          <t>Richmond Park</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>St. Peter's</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>st-peter-s-rhoden-hall-clarendon</t>
+          <t>all-saints-richmond-park-clarendon</t>
         </is>
       </c>
     </row>
@@ -13190,12 +13190,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Richmond Park</t>
+          <t>Rock River</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>St. James'</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>all-saints-richmond-park-clarendon</t>
+          <t>st-james-rock-river-clarendon</t>
         </is>
       </c>
     </row>
@@ -13237,12 +13237,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Rock River</t>
+          <t>Rocky Point</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>St. James'</t>
+          <t>St. Andrew's</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>st-james-rock-river-clarendon</t>
+          <t>st-andrew-s-rocky-point-clarendon</t>
         </is>
       </c>
     </row>
@@ -13284,12 +13284,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Rocky Point</t>
+          <t>Sanguinetti</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>St. Andrew's</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -13302,24 +13302,24 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F266" s="5" t="inlineStr">
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G266" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H266" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G266" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H266" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>st-andrew-s-rocky-point-clarendon</t>
+          <t>st-luke-s-sanguinetti-clarendon</t>
         </is>
       </c>
     </row>
@@ -13331,22 +13331,22 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Sanguinetti</t>
+          <t>The Cross</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>Church of the White Cross (Ruins)</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>ruin</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>ruin</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>st-luke-s-sanguinetti-clarendon</t>
+          <t>church-of-the-white-cross-ruins-the-cross-clarendon</t>
         </is>
       </c>
     </row>
@@ -13378,22 +13378,22 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>The Cross</t>
+          <t>Toll Gate</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Church of the White Cross (Ruins)</t>
+          <t>St. James'</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ruin</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>ruin</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>church-of-the-white-cross-ruins-the-cross-clarendon</t>
+          <t>st-james-s-toll-gate-clarendon</t>
         </is>
       </c>
     </row>
@@ -13425,17 +13425,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Toll Gate</t>
+          <t>Wood Hall</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>St. James'</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>chapel</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -13443,46 +13443,46 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F269" s="5" t="inlineStr">
+      <c r="F269" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G269" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H269" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G269" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H269" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>st-james-s-toll-gate-clarendon</t>
+          <t>st-luke-s-wood-hall-clarendon</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Clarendon</t>
+          <t>St. Catherine</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Wood Hall</t>
+          <t>Bartons</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>chapel</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -13490,24 +13490,24 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F270" s="5" t="inlineStr">
+      <c r="F270" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G270" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H270" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G270" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H270" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>st-luke-s-wood-hall-clarendon</t>
+          <t>st-george-s-bartons-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13519,12 +13519,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Bartons</t>
+          <t>Bellas Gate</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -13547,14 +13547,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H271" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H271" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>st-george-s-bartons-st-catherine</t>
+          <t>all-saints-bellas-gate-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13566,12 +13564,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Bellas Gate</t>
+          <t>Blackstonedge</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -13581,7 +13579,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
@@ -13594,12 +13592,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H272" s="4" t="n">
-        <v>1</v>
+      <c r="H272" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>all-saints-bellas-gate-st-catherine</t>
+          <t>st-george-s-blackstonedge-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13611,12 +13611,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Blackstonedge</t>
+          <t>Bog Walk</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>St. Thomas-ye-Vale</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
@@ -13639,14 +13639,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H273" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H273" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>st-george-s-blackstonedge-st-catherine</t>
+          <t>st-thomas-ye-vale-bog-walk-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13658,12 +13656,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Bog Walk</t>
+          <t>Camperdown</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>St. Thomas-ye-Vale</t>
+          <t>St. Lawrence's</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13686,12 +13684,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H274" s="4" t="n">
-        <v>6</v>
+      <c r="H274" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>st-thomas-ye-vale-bog-walk-st-catherine</t>
+          <t>st-lawrence-s-camperdown-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13703,12 +13703,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Camperdown</t>
+          <t>Clapham</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>St. Lawrence's</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13721,24 +13721,24 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F275" s="5" t="inlineStr">
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G275" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H275" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>st-lawrence-s-camperdown-st-catherine</t>
+          <t>st-paul-s-clapham-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Clapham</t>
+          <t>Crescent</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. Barnabas'</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13768,24 +13768,24 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F276" s="5" t="inlineStr">
+      <c r="F276" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G276" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G276" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H276" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>st-paul-s-clapham-st-catherine</t>
+          <t>st-barnabas-crescent-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13797,12 +13797,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Crescent</t>
+          <t>Ewarton</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>St. Barnabas'</t>
+          <t>SS Simon and Jude</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13825,14 +13825,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H277" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H277" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>st-barnabas-crescent-st-catherine</t>
+          <t>ss-simon-and-jude-ewarton-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13844,12 +13842,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Ewarton</t>
+          <t>Faith's</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>SS Simon and Jude</t>
+          <t>St. Faith's</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13872,12 +13870,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H278" s="4" t="n">
-        <v>3</v>
+      <c r="H278" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>ss-simon-and-jude-ewarton-st-catherine</t>
+          <t>st-faith-s-faith-s-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13889,12 +13889,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Faith's</t>
+          <t>Freetown</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>St. Faith's</t>
+          <t>SS Michael and George's</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>st-faith-s-faith-s-st-catherine</t>
+          <t>ss-michael-and-george-s-freetown-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13936,42 +13936,42 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Freetown</t>
+          <t>Goffe / Goba (district)</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>SS Michael and George's</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F280" s="5" t="inlineStr">
+          <t>inactive</t>
+        </is>
+      </c>
+      <c r="F280" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G280" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H280" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G280" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H280" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>ss-michael-and-george-s-freetown-st-catherine</t>
+          <t>st-paul-s-goba-st-catherine</t>
         </is>
       </c>
     </row>
@@ -13983,22 +13983,22 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Goffe / Goba (district)</t>
+          <t>Guanaboa Vale</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. John's OPC</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
@@ -14011,14 +14011,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H281" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H281" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>st-paul-s-goba-st-catherine</t>
+          <t>st-john-s-opc-guanaboa-vale-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14030,12 +14028,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Guanaboa Vale</t>
+          <t>Guy's Hill</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>St. John's OPC</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -14058,12 +14056,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H282" s="4" t="n">
-        <v>1</v>
+      <c r="H282" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>st-john-s-opc-guanaboa-vale-st-catherine</t>
+          <t>all-saints-guys-hill-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14075,12 +14075,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Guy's Hill</t>
+          <t>Ham Walk</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>St. Mark's</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -14093,24 +14093,24 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F283" s="5" t="inlineStr">
+      <c r="F283" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G283" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G283" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H283" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>all-saints-guys-hill-st-catherine</t>
+          <t>st-mark-s-ham-walk-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14122,12 +14122,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Ham Walk</t>
+          <t>Harewood</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>St. Mark's</t>
+          <t>St. Saviour's</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>st-mark-s-ham-walk-st-catherine</t>
+          <t>st-saviour-s-harewood-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14169,12 +14169,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Harewood</t>
+          <t>Innswood/McCook's Pen</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>St. Saviour's</t>
+          <t>St. Joseph's</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>st-saviour-s-harewood-st-catherine</t>
+          <t>st-joseph-s-innswood-mccook-s-pen-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14216,12 +14216,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Innswood/McCook's Pen</t>
+          <t>Juan-de-Bolas</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>St. Joseph's</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>st-joseph-s-innswood-mccook-s-pen-st-catherine</t>
+          <t>st-luke-s-juan-de-bolas-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14263,12 +14263,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Juan-de-Bolas</t>
+          <t>Kentish</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -14281,24 +14281,24 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F287" s="5" t="inlineStr">
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H287" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G287" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H287" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>st-luke-s-juan-de-bolas-st-catherine</t>
+          <t>st-paul-s-kentish-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14310,12 +14310,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Kentish</t>
+          <t>Linstead</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>Church of the Holy Trinity</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -14328,24 +14328,22 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F288" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G288" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H288" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F288" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G288" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H288" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>st-paul-s-kentish-st-catherine</t>
+          <t>church-of-the-holy-trinity-linstead-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14362,7 +14360,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Church of the Holy Trinity</t>
+          <t>St. John's Church</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -14385,12 +14383,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H289" s="4" t="n">
-        <v>1</v>
+      <c r="H289" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>church-of-the-holy-trinity-linstead-st-catherine</t>
+          <t>st-john-s-church-linstead-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14402,12 +14402,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Linstead</t>
+          <t>Lluidas Vale</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>St. John's Church</t>
+          <t>St. Peter's</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
@@ -14430,14 +14430,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H290" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H290" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>st-john-s-church-linstead-st-catherine</t>
+          <t>st-peter-s-lluidas-vale-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14449,12 +14447,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Lluidas Vale</t>
+          <t>Macca Tree</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>St. Peter's</t>
+          <t>St. Mark's</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -14464,7 +14462,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
@@ -14477,12 +14475,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H291" s="4" t="n">
-        <v>5</v>
+      <c r="H291" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>st-peter-s-lluidas-vale-st-catherine</t>
+          <t>st-mark-s-macca-tree-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14494,12 +14494,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Macca Tree</t>
+          <t>Marley Hill</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>St. Mark's</t>
+          <t>St. Andrew's</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -14522,14 +14522,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H292" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H292" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>st-mark-s-macca-tree-st-catherine</t>
+          <t>st-andrew-s-marley-hill-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14541,12 +14539,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Marley Hill</t>
+          <t>Morris Hall</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>St. Andrew's</t>
+          <t>St. Phillip's</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -14570,11 +14568,11 @@
         </is>
       </c>
       <c r="H293" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>st-andrew-s-marley-hill-st-catherine</t>
+          <t>st-phillip-s-morris-hall-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14586,12 +14584,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Morris Hall</t>
+          <t>Mount Industry</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>St. Phillip's</t>
+          <t>St. Boniface</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -14614,12 +14612,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H294" s="4" t="n">
-        <v>1</v>
+      <c r="H294" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>st-phillip-s-morris-hall-st-catherine</t>
+          <t>st-boniface-mount-industry-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14631,12 +14631,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Mount Industry</t>
+          <t>Mount Moreland</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>St. Boniface</t>
+          <t>St. Matthew's</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>st-boniface-mount-industry-st-catherine</t>
+          <t>st-matthew-s-mt-moorland-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14678,12 +14678,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Mount Moreland</t>
+          <t>Old Harbour</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>St. Matthew's</t>
+          <t>Holy Trinity</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -14693,7 +14693,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>st-matthew-s-mt-moorland-st-catherine</t>
+          <t>holy-trinity-old-harbour-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Holy Trinity</t>
+          <t>St. Dorothy's Church</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
@@ -14753,14 +14753,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H297" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H297" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>holy-trinity-old-harbour-st-catherine</t>
+          <t>st-dorothy-s-church-old-harbour-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14772,12 +14770,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Old Harbour</t>
+          <t>Old Harbour Bay</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>St. Dorothy's Church</t>
+          <t>St. Philip's</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14801,11 +14799,11 @@
         </is>
       </c>
       <c r="H298" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>st-dorothy-s-church-old-harbour-st-catherine</t>
+          <t>st-philip-s-old-harbour-bay-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14817,12 +14815,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Old Harbour Bay</t>
+          <t>Old Works</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>St. Philip's</t>
+          <t>St. Peter's</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14845,12 +14843,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H299" s="4" t="n">
-        <v>1</v>
+      <c r="H299" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>st-philip-s-old-harbour-bay-st-catherine</t>
+          <t>st-peter-s-old-works-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14862,12 +14862,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Old Works</t>
+          <t>Point Hill</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>St. Peter's</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14890,14 +14890,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H300" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H300" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>st-peter-s-old-works-st-catherine</t>
+          <t>st-george-s-point-hill-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14909,12 +14907,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Point Hill</t>
+          <t>Portmore</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>Church of Reconciliation</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14937,12 +14935,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H301" s="4" t="n">
-        <v>1</v>
+      <c r="H301" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>st-george-s-point-hill-st-catherine</t>
+          <t>church-of-reconciliation-portmore-st-catherine</t>
         </is>
       </c>
     </row>
@@ -14954,12 +14954,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Portmore</t>
+          <t>Sligoville</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Church of Reconciliation</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14972,24 +14972,22 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F302" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G302" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H302" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G302" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H302" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>church-of-reconciliation-portmore-st-catherine</t>
+          <t>st-john-s-sligoville-st-catherine</t>
         </is>
       </c>
     </row>
@@ -15001,12 +14999,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Sligoville</t>
+          <t>Spanish Town</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>Holy Trinity</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -15016,7 +15014,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
@@ -15029,12 +15027,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H303" s="4" t="n">
-        <v>4</v>
+      <c r="H303" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>st-john-s-sligoville-st-catherine</t>
+          <t>holy-trinity-spanish-town-st-catherine</t>
         </is>
       </c>
     </row>
@@ -15051,17 +15051,17 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Holy Trinity</t>
+          <t>St. Jago de la Vega (The Cathedral)</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>cathedral</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
@@ -15074,14 +15074,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H304" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H304" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>holy-trinity-spanish-town-st-catherine</t>
+          <t>st-jago-de-la-vega-the-cathedral-spanish-town-st-catherine</t>
         </is>
       </c>
     </row>
@@ -15093,17 +15091,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Spanish Town</t>
+          <t>Top Hill</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>St. Jago de la Vega (The Cathedral)</t>
+          <t>St. Simon's</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>cathedral</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -15121,12 +15119,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H305" s="4" t="n">
-        <v>2</v>
+      <c r="H305" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>st-jago-de-la-vega-the-cathedral-spanish-town-st-catherine</t>
+          <t>st-simon-s-top-hill-st-catherine</t>
         </is>
       </c>
     </row>
@@ -15138,12 +15138,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Top Hill</t>
+          <t>Watermount</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>St. Simon's</t>
+          <t>St. Augustine's</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -15156,76 +15156,29 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F306" s="5" t="inlineStr">
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G306" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H306" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G306" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H306" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>st-simon-s-top-hill-st-catherine</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>St. Catherine</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Watermount</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>St. Augustine's</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F307" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G307" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H307" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
           <t>st-augustine-s-watermount-st-catherine</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I307"/>
+  <autoFilter ref="A1:I306"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15236,7 +15189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I192"/>
+  <dimension ref="A1:I185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15440,16 +15393,8 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>missing</t>
@@ -15508,17 +15453,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Craighton</t>
+          <t>Cross Roads</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Mark’s</t>
+          <t>St. Luke's Church</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>chapel</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -15526,20 +15471,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>st-mark-s-craighton-st-andrew</t>
+          <t>st-luke-s-church-cross-roads-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15551,12 +15492,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cross Roads</t>
+          <t>Duhaney Park</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>St. Luke's Church</t>
+          <t>Church of the Resurrection</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15578,7 +15519,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>st-luke-s-church-cross-roads-st-andrew</t>
+          <t>church-of-the-resurrection-duhaney-park-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15590,12 +15531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Duhaney Park</t>
+          <t>Havendale</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Church of the Resurrection</t>
+          <t>Church of the Transfiguration</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15617,7 +15558,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>church-of-the-resurrection-duhaney-park-st-andrew</t>
+          <t>church-of-the-transfiguration-havendale-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15629,22 +15570,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Havendale</t>
+          <t>Hunt's Bay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Church of the Transfiguration</t>
+          <t>St. Cuthbert's</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -15656,7 +15597,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>church-of-the-transfiguration-havendale-st-andrew</t>
+          <t>st-cuthbert-s-hunt-s-bay-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15668,22 +15609,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hunt's Bay</t>
+          <t>Jack's Hill</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Cuthbert's</t>
+          <t>St. Matthew's</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -15695,7 +15636,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>st-cuthbert-s-hunt-s-bay-st-andrew</t>
+          <t>st-matthew-s-jack-s-hill-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15707,12 +15648,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jack's Hill</t>
+          <t>Kencot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Matthew's</t>
+          <t>St. Clement's</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15734,7 +15675,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>st-matthew-s-jack-s-hill-st-andrew</t>
+          <t>st-clement-s-kencot-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15746,17 +15687,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kencot</t>
+          <t>Lawrencefield</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Clement's</t>
+          <t>St. Mary's Chapel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>chapel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -15773,7 +15714,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>st-clement-s-kencot-st-andrew</t>
+          <t>st-mary-s-chapel-lawrencefield-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15785,17 +15726,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lawrencefield</t>
+          <t>Majesty Gardens</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>St. Mary's Chapel</t>
+          <t>St. Thomas Mission</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>chapel</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -15812,7 +15753,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>st-mary-s-chapel-lawrencefield-st-andrew</t>
+          <t>st-thomas-mission-majesty-gardens-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15824,17 +15765,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Majesty Gardens</t>
+          <t>Marverly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>St. Thomas Mission</t>
+          <t>St. Mary the Virgin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -15851,7 +15792,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>st-thomas-mission-majesty-gardens-st-andrew</t>
+          <t>st-mary-the-virgin-marverly-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15863,12 +15804,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Marverly</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>St. Mary the Virgin</t>
+          <t>St. Stephen's</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15890,7 +15831,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>st-mary-the-virgin-marverly-st-andrew</t>
+          <t>st-stephen-s-maryland-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15902,12 +15843,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Mavis Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>St. Stephen's</t>
+          <t>St. Michael's</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15929,7 +15870,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>st-stephen-s-maryland-st-andrew</t>
+          <t>st-michael-s-mavis-bank-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15941,12 +15882,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mavis Bank</t>
+          <t>Merrivale</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>St. Michael's</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15968,7 +15909,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>st-michael-s-mavis-bank-st-andrew</t>
+          <t>st-john-s-merrivale-st-andrew</t>
         </is>
       </c>
     </row>
@@ -15980,12 +15921,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Merrivale</t>
+          <t>Mona</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>Church of Ascension</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -16007,7 +15948,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>st-john-s-merrivale-st-andrew</t>
+          <t>church-of-ascension-mona-st-andrew</t>
         </is>
       </c>
     </row>
@@ -16019,12 +15960,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mona</t>
+          <t>Padmore</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Church of Ascension</t>
+          <t>St. Martin's</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -16046,7 +15987,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>church-of-ascension-mona-st-andrew</t>
+          <t>st-martin-s-padmore-st-andrew</t>
         </is>
       </c>
     </row>
@@ -16058,12 +15999,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Padmore</t>
+          <t>The Grove</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Martin's</t>
+          <t>St. Joseph's</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -16085,7 +16026,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>st-martin-s-padmore-st-andrew</t>
+          <t>st-joseph-s-the-grove-st-andrew</t>
         </is>
       </c>
     </row>
@@ -16097,12 +16038,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Grove</t>
+          <t>Tom's River</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Joseph's</t>
+          <t>St. Bartholomew's</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -16124,7 +16065,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>st-joseph-s-the-grove-st-andrew</t>
+          <t>st-bartholomew-s-tom-s-river-st-andrew</t>
         </is>
       </c>
     </row>
@@ -16136,12 +16077,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tom's River</t>
+          <t>Tower Hill</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>St. Bartholomew's</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -16163,7 +16104,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>st-bartholomew-s-tom-s-river-st-andrew</t>
+          <t>st-paul-s-tower-hill-st-andrew</t>
         </is>
       </c>
     </row>
@@ -16175,12 +16116,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tower Hill</t>
+          <t>Whitfield Town</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. Philip's</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -16202,29 +16143,29 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>st-paul-s-tower-hill-st-andrew</t>
+          <t>st-philip-s-whitfield-town-st-andrew</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>St. Andrew</t>
+          <t>St. Thomas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Whitfield Town</t>
+          <t>Bull Bay</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>St. Philip's</t>
+          <t>St. Martin's Mission</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -16241,7 +16182,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>st-philip-s-whitfield-town-st-andrew</t>
+          <t>st-martin-s-mission-bull-bay-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16253,17 +16194,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bull Bay</t>
+          <t>Danvers Pen</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>St. Martin's Mission</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -16271,24 +16212,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>st-martin-s-mission-bull-bay-st-thomas</t>
+          <t>st-paul-s-danvers-pen-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16300,12 +16233,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Danvers Pen</t>
+          <t>Golden Grove</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. Andrew's</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -16327,7 +16260,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>st-paul-s-danvers-pen-st-thomas</t>
+          <t>st-andrew-s-golden-grove-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16339,12 +16272,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Golden Grove</t>
+          <t>Leith Hall</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>St. Andrew's</t>
+          <t>St. John's Church (Old)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -16354,7 +16287,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>ruin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -16366,7 +16299,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>st-andrew-s-golden-grove-st-thomas</t>
+          <t>st-john-s-church-old-leith-hall-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16378,12 +16311,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Leith Hall</t>
+          <t>Middleton</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. John's Church (Old)</t>
+          <t>St. Matthias'</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -16393,7 +16326,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ruin</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -16405,7 +16338,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>st-john-s-church-old-leith-hall-st-thomas</t>
+          <t>st-matthias-middleton-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16417,12 +16350,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Middleton</t>
+          <t>Mt. Felix</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Matthias'</t>
+          <t>St. Augustine's</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -16435,24 +16368,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>st-matthias-middleton-st-thomas</t>
+          <t>st-augustine-s-mt-felix-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16464,12 +16389,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mt. Felix</t>
+          <t>The Abbey</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Augustine's</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -16491,7 +16416,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>st-augustine-s-mt-felix-st-thomas</t>
+          <t>all-saints-the-abbey-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16503,12 +16428,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Abbey</t>
+          <t>Thornton</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>St. Stephen's</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -16530,7 +16455,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>all-saints-the-abbey-st-thomas</t>
+          <t>st-stephen-s-thornton-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16542,12 +16467,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thornton</t>
+          <t>Trinityville</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Stephen's</t>
+          <t>Church of the Holy Trinity</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -16569,7 +16494,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>st-stephen-s-thornton-st-thomas</t>
+          <t>holy-trinity-trinityville-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16581,12 +16506,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Trinityville</t>
+          <t>Whitehall</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Church of the Holy Trinity</t>
+          <t>St. Boniface's</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -16599,24 +16524,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>holy-trinity-trinityville-st-thomas</t>
+          <t>st-boniface-whitehall-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16628,12 +16545,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Whitehall</t>
+          <t>Wilmington</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Boniface's</t>
+          <t>St. Matthew's</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -16646,24 +16563,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>st-boniface-whitehall-st-thomas</t>
+          <t>st-matthew-s-wilmington-st-thomas</t>
         </is>
       </c>
     </row>
@@ -16675,12 +16584,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wilmington</t>
+          <t>Woburn Lawn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Matthew's</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -16693,41 +16602,33 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>st-matthew-s-wilmington-st-thomas</t>
+          <t>st-john-s-woburn-lawn-st-thomas</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>St. Thomas</t>
+          <t>Portland</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Woburn Lawn</t>
+          <t>Bangor Ridge</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>St. Philip's</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -16749,7 +16650,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>st-john-s-woburn-lawn-st-thomas</t>
+          <t>st-philip-s-bangor-ridge-portland</t>
         </is>
       </c>
     </row>
@@ -16761,12 +16662,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bangor Ridge</t>
+          <t>Belvedere</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Philip's</t>
+          <t>St. Joseph's</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -16788,7 +16689,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>st-philip-s-bangor-ridge-portland</t>
+          <t>st-joseph-s-belvedere-portland</t>
         </is>
       </c>
     </row>
@@ -16800,12 +16701,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Belvedere</t>
+          <t>Birnamwood</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Joseph's</t>
+          <t>St. James'</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -16827,7 +16728,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>st-joseph-s-belvedere-portland</t>
+          <t>st-james-birnamwood-portland</t>
         </is>
       </c>
     </row>
@@ -16839,17 +16740,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Birnamwood</t>
+          <t>Boundbrook</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. James'</t>
+          <t>Boundbrook Chapel-of-Ease</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>chapel</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -16866,7 +16767,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>st-james-birnamwood-portland</t>
+          <t>boundbrook-chapel-of-ease-boundbrook-portland</t>
         </is>
       </c>
     </row>
@@ -16878,17 +16779,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Boundbrook</t>
+          <t>Bourbon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boundbrook Chapel-of-Ease</t>
+          <t>St. Jude's</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>chapel</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -16905,7 +16806,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>boundbrook-chapel-of-ease-boundbrook-portland</t>
+          <t>st-jude-s-bourbon-portland</t>
         </is>
       </c>
     </row>
@@ -16917,12 +16818,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bourbon</t>
+          <t>Bybrook</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Jude's</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -16944,7 +16845,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>st-jude-s-bourbon-portland</t>
+          <t>st-john-s-bybrook-portland</t>
         </is>
       </c>
     </row>
@@ -16956,12 +16857,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bybrook</t>
+          <t>Claverty Cottage</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -16983,7 +16884,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>st-john-s-bybrook-portland</t>
+          <t>st-paul-s-claverty-cottage-portland</t>
         </is>
       </c>
     </row>
@@ -16995,12 +16896,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Claverty Cottage</t>
+          <t>Comfort Castle</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -17022,7 +16923,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>st-paul-s-claverty-cottage-portland</t>
+          <t>st-luke-s-comfort-castle-portland</t>
         </is>
       </c>
     </row>
@@ -17034,12 +16935,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Comfort Castle</t>
+          <t>Cooper's Hill</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -17061,7 +16962,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>st-luke-s-comfort-castle-portland</t>
+          <t>st-john-s-cooper-s-hill-portland</t>
         </is>
       </c>
     </row>
@@ -17073,12 +16974,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cooper's Hill</t>
+          <t>Fellowship</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -17100,7 +17001,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>st-john-s-cooper-s-hill-portland</t>
+          <t>all-saints-fellowship-portland</t>
         </is>
       </c>
     </row>
@@ -17112,12 +17013,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fellowship</t>
+          <t>Fruitful Vale</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>St. Michael's</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -17139,7 +17040,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>all-saints-fellowship-portland</t>
+          <t>st-michael-s-fruitful-vale-portland</t>
         </is>
       </c>
     </row>
@@ -17151,7 +17052,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fruitful Vale</t>
+          <t>John's Hall</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -17178,7 +17079,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>st-michael-s-fruitful-vale-portland</t>
+          <t>st-michael-s-john-s-hall-portland</t>
         </is>
       </c>
     </row>
@@ -17190,17 +17091,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>John's Hall</t>
+          <t>Maidstone</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>St. Michael's</t>
+          <t>Maidstone Chapel</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>chapel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -17217,7 +17118,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>st-michael-s-john-s-hall-portland</t>
+          <t>maidstone-chapel-portland</t>
         </is>
       </c>
     </row>
@@ -17229,17 +17130,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Maidstone</t>
+          <t>Moore Town</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Maidstone Chapel</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>chapel</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -17247,24 +17148,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>maidstone-chapel-portland</t>
+          <t>st-paul-s-moore-town-portland</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17169,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Moore Town</t>
+          <t>Nonsuch</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -17303,7 +17196,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>st-paul-s-moore-town-portland</t>
+          <t>st-paul-s-nonsuch-portland</t>
         </is>
       </c>
     </row>
@@ -17320,17 +17213,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. Peter's Chapel (Ruin)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>chapel</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>ruin</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -17342,7 +17235,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>st-paul-s-nonsuch-portland</t>
+          <t>st-peter-s-chapel-ruin-nonsuch-portland</t>
         </is>
       </c>
     </row>
@@ -17354,22 +17247,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nonsuch</t>
+          <t>Rose Hill</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>St. Peter's Chapel (Ruin)</t>
+          <t>St. Mary's</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>chapel</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ruin</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -17381,7 +17274,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>st-peter-s-chapel-ruin-nonsuch-portland</t>
+          <t>st-mary-s-rose-hill-portland</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17286,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rose Hill</t>
+          <t>Rural Hill</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -17411,24 +17304,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>st-mary-s-rose-hill-portland</t>
+          <t>st-mary-s-rural-hill-portland</t>
         </is>
       </c>
     </row>
@@ -17440,12 +17325,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rural Hill</t>
+          <t>Sherwood Forest</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>St. Mary's</t>
+          <t>St. Christopher's</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -17467,7 +17352,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>st-mary-s-rural-hill-portland</t>
+          <t>st-christopher-s-sherwood-forest-portland</t>
         </is>
       </c>
     </row>
@@ -17479,12 +17364,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sherwood Forest</t>
+          <t>Windsor Forrest</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>St. Christopher's</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -17506,24 +17391,24 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>st-christopher-s-sherwood-forest-portland</t>
+          <t>st-john-s-windsor-forrest-portland</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Portland</t>
+          <t>St. Mary</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Windsor Forrest</t>
+          <t>Albion Mountain</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>St. Alban's</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -17545,7 +17430,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>st-john-s-windsor-forrest-portland</t>
+          <t>st-alban-s-albion-mountain-st-mary</t>
         </is>
       </c>
     </row>
@@ -17557,12 +17442,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Albion Mountain</t>
+          <t>Bonny Gate</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>St. Alban's</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -17584,7 +17469,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>st-alban-s-albion-mountain-st-mary</t>
+          <t>st-luke-s-bonny-gate-st-mary</t>
         </is>
       </c>
     </row>
@@ -17596,12 +17481,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bonny Gate</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>St. Agatha's</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -17623,7 +17508,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>st-luke-s-bonny-gate-st-mary</t>
+          <t>st-agatha-s-bromley-st-mary</t>
         </is>
       </c>
     </row>
@@ -17635,12 +17520,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Clifton Lodge</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Agatha's</t>
+          <t>St. Margaret's</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -17662,7 +17547,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>st-agatha-s-bromley-st-mary</t>
+          <t>st-margaret-s-clifton-lodge-st-mary</t>
         </is>
       </c>
     </row>
@@ -17674,12 +17559,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Clifton Lodge</t>
+          <t>Devon Pen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Margaret's</t>
+          <t>St. Patrick's</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -17701,7 +17586,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>st-margaret-s-clifton-lodge-st-mary</t>
+          <t>st-patrick-s-devon-pen-st-mary</t>
         </is>
       </c>
     </row>
@@ -17713,12 +17598,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Devon Pen</t>
+          <t>Enfield</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>St. Patrick's</t>
+          <t>St. Barnabas'</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -17740,7 +17625,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>st-patrick-s-devon-pen-st-mary</t>
+          <t>st-barnabas-enfield-st-mary</t>
         </is>
       </c>
     </row>
@@ -17752,12 +17637,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Enfield</t>
+          <t>Galina</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>St. Barnabas'</t>
+          <t>St. Peter's</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -17779,7 +17664,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>st-barnabas-enfield-st-mary</t>
+          <t>st-peter-s-galina-st-mary</t>
         </is>
       </c>
     </row>
@@ -17791,12 +17676,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Galina</t>
+          <t>Gayle</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>St. Peter's</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -17809,24 +17694,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>st-peter-s-galina-st-mary</t>
+          <t>st-john-s-gayle-st-mary</t>
         </is>
       </c>
     </row>
@@ -17838,12 +17715,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gayle</t>
+          <t>Highgate</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>St. Cyprian's</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -17865,7 +17742,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>st-john-s-gayle-st-mary</t>
+          <t>st-cyprian-s-highgate-st-mary</t>
         </is>
       </c>
     </row>
@@ -17877,12 +17754,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Highgate</t>
+          <t>Labyrinth</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>St. Cyprian's</t>
+          <t>St. Andrew's</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -17904,7 +17781,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>st-cyprian-s-highgate-st-mary</t>
+          <t>st-andrew-s-labyrinth-st-mary</t>
         </is>
       </c>
     </row>
@@ -17916,12 +17793,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Labyrinth</t>
+          <t>Long Road</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Andrew's</t>
+          <t>St. Margaret's</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -17943,7 +17820,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>st-andrew-s-labyrinth-st-mary</t>
+          <t>st-margaret-s-long-road-st-mary</t>
         </is>
       </c>
     </row>
@@ -17955,12 +17832,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Long Road</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Margaret's</t>
+          <t>St. Martin's</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -17982,7 +17859,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>st-margaret-s-long-road-st-mary</t>
+          <t>st-martin-s-martin-st-mary</t>
         </is>
       </c>
     </row>
@@ -17994,12 +17871,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mason Hall</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>St. Martin's</t>
+          <t>St. Elizabeth's</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -18021,7 +17898,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>st-martin-s-martin-st-mary</t>
+          <t>st-elizabeth-s-mason-hall-st-mary</t>
         </is>
       </c>
     </row>
@@ -18033,12 +17910,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mason Hall</t>
+          <t>Retreat</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>St. Elizabeth's</t>
+          <t>Holy Trinity</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -18060,7 +17937,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>st-elizabeth-s-mason-hall-st-mary</t>
+          <t>holy-trinity-retreat-st-mary</t>
         </is>
       </c>
     </row>
@@ -18072,12 +17949,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Retreat</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Holy Trinity</t>
+          <t>Church of the Epiphany</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -18099,7 +17976,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>holy-trinity-retreat-st-mary</t>
+          <t>church-of-the-epiphany-richmond-st-mary</t>
         </is>
       </c>
     </row>
@@ -18111,12 +17988,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Rio Nuevo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Church of the Epiphany</t>
+          <t>St. Mary's Church (Old)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -18126,7 +18003,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>ruin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -18138,7 +18015,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>church-of-the-epiphany-richmond-st-mary</t>
+          <t>st-mary-s-church-old-rio-nuevo-st-mary</t>
         </is>
       </c>
     </row>
@@ -18150,12 +18027,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Rio Nuevo</t>
+          <t>Scott's Hall</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>St. Mary's Church (Old)</t>
+          <t>St. Mark's</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -18165,7 +18042,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ruin</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -18177,7 +18054,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>st-mary-s-church-old-rio-nuevo-st-mary</t>
+          <t>st-mark-s-scott-s-hall-st-mary</t>
         </is>
       </c>
     </row>
@@ -18189,12 +18066,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Scott's Hall</t>
+          <t>Woodside</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>St. Mark's</t>
+          <t>St. Gabriel's</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -18216,24 +18093,24 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>st-mark-s-scott-s-hall-st-mary</t>
+          <t>st-gabriel-s-woodside-st-mary</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>St. Mary</t>
+          <t>St. Ann</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Woodside</t>
+          <t>Bamboo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>St. Gabriel's</t>
+          <t>St. Andrew's</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -18255,7 +18132,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>st-gabriel-s-woodside-st-mary</t>
+          <t>st-andrew-s-bamboo-st-ann</t>
         </is>
       </c>
     </row>
@@ -18267,12 +18144,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bamboo</t>
+          <t>Brittonville</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>St. Andrew's</t>
+          <t>St. David's</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -18294,7 +18171,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>st-andrew-s-bamboo-st-ann</t>
+          <t>st-david-s-brittonville-st-ann</t>
         </is>
       </c>
     </row>
@@ -18306,17 +18183,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Brittonville</t>
+          <t>Chalky Hill</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>St. David's</t>
+          <t>St. John's Mission</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -18333,7 +18210,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>st-david-s-brittonville-st-ann</t>
+          <t>st-john-s-mission-chalky-hill-st-ann</t>
         </is>
       </c>
     </row>
@@ -18345,17 +18222,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Chalky Hill</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>St. John's Mission</t>
+          <t>St. Mark's</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -18372,7 +18249,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>st-john-s-mission-chalky-hill-st-ann</t>
+          <t>st-mark-s-chester-st-ann</t>
         </is>
       </c>
     </row>
@@ -18384,12 +18261,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Claremont</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>St. Mark's</t>
+          <t>St. Matthew's</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -18411,7 +18288,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>st-mark-s-chester-st-ann</t>
+          <t>st-matthew-s-claremont-st-ann</t>
         </is>
       </c>
     </row>
@@ -18423,12 +18300,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Claremont</t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Matthew's</t>
+          <t>St. James'</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -18450,7 +18327,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>st-matthew-s-claremont-st-ann</t>
+          <t>st-james-gibraltar-st-ann</t>
         </is>
       </c>
     </row>
@@ -18462,12 +18339,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gibraltar</t>
+          <t>Hiattsfield</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>St. James'</t>
+          <t>St. Francis Church</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -18489,7 +18366,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>st-james-gibraltar-st-ann</t>
+          <t>st-francis-church-hiattsfield-st-ann</t>
         </is>
       </c>
     </row>
@@ -18501,12 +18378,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hiattsfield</t>
+          <t>Lime Hall</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>St. Francis Church</t>
+          <t>St. Saviour's</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -18528,7 +18405,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>st-francis-church-hiattsfield-st-ann</t>
+          <t>st-saviour-s-lime-hall-st-ann</t>
         </is>
       </c>
     </row>
@@ -18540,12 +18417,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lime Hall</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>St. Saviour's</t>
+          <t>St. Barnabas'</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -18567,7 +18444,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>st-saviour-s-lime-hall-st-ann</t>
+          <t>st-barnabas-madras-st-ann</t>
         </is>
       </c>
     </row>
@@ -18579,12 +18456,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Ocho Rios</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>St. Barnabas'</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -18606,7 +18483,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>st-barnabas-madras-st-ann</t>
+          <t>st-john-s-ocho-rios-st-ann</t>
         </is>
       </c>
     </row>
@@ -18618,12 +18495,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ocho Rios</t>
+          <t>Prickly Pole</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>St. Andrew's</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -18645,7 +18522,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>st-john-s-ocho-rios-st-ann</t>
+          <t>st-andrew-s-prickly-pole-st-ann</t>
         </is>
       </c>
     </row>
@@ -18657,12 +18534,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Prickly Pole</t>
+          <t>Salisbury</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>St. Andrew's</t>
+          <t>St. Agnes</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -18684,24 +18561,24 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>st-andrew-s-prickly-pole-st-ann</t>
+          <t>st-agnes-salisbury-st-ann</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>St. Ann</t>
+          <t>Trelawny</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>St. Agnes</t>
+          <t>St. Barnabas'</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -18723,24 +18600,24 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>st-agnes-salisbury-st-ann</t>
+          <t>st-barnabas-duncan-trelawny</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Trelawny</t>
+          <t>St. James</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Blue Hole</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>St. Barnabas'</t>
+          <t>St. Leonard's</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -18762,7 +18639,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>st-barnabas-duncan-trelawny</t>
+          <t>st-leonard-s-blue-hole-st-james</t>
         </is>
       </c>
     </row>
@@ -18774,12 +18651,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Blue Hole</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>St. Leonard's</t>
+          <t>St. Stephen's</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -18801,7 +18678,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>st-leonard-s-blue-hole-st-james</t>
+          <t>st-stephen-s-cambridge-st-james</t>
         </is>
       </c>
     </row>
@@ -18813,12 +18690,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Coral Gardens</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>St. Stephen's</t>
+          <t>St. Augustine's</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18831,24 +18708,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>st-stephen-s-cambridge-st-james</t>
+          <t>st-augustine-s-coral-gardens-st-james</t>
         </is>
       </c>
     </row>
@@ -18860,17 +18729,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Coral Gardens</t>
+          <t>Cornwall Mountain</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>St. Augustine's</t>
+          <t>St. Stephen's Mission</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -18878,24 +18747,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>st-augustine-s-coral-gardens-st-james</t>
+          <t>st-stephen-s-cornwall-mountain-st-james</t>
         </is>
       </c>
     </row>
@@ -18907,12 +18768,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cornwall Mountain</t>
+          <t>Glendevon</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>St. Stephen's Mission</t>
+          <t>St. Francis'</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18934,7 +18795,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>st-stephen-s-cornwall-mountain-st-james</t>
+          <t>st-francis-glendevon-st-james</t>
         </is>
       </c>
     </row>
@@ -18946,17 +18807,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Glendevon</t>
+          <t>Grace Hill</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>St. Francis'</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -18973,7 +18834,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>st-francis-glendevon-st-james</t>
+          <t>st-john-s-grace-hill-st-james</t>
         </is>
       </c>
     </row>
@@ -18985,12 +18846,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Grace Hill</t>
+          <t>Granville</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>Mary Magdalene</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -19012,7 +18873,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>st-john-s-grace-hill-st-james</t>
+          <t>mary-magdalene-granville-st-james</t>
         </is>
       </c>
     </row>
@@ -19024,12 +18885,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Granville</t>
+          <t>Hopewell</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mary Magdalene</t>
+          <t>St. Mark's</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19051,7 +18912,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>mary-magdalene-granville-st-james</t>
+          <t>st-mark-s-hopewell-st-james</t>
         </is>
       </c>
     </row>
@@ -19063,12 +18924,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hopewell</t>
+          <t>Mount Salem</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>St. Mark's</t>
+          <t>Holy Cross</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19081,24 +18942,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>st-mark-s-hopewell-st-james</t>
+          <t>holy-cross-mount-salem-st-james</t>
         </is>
       </c>
     </row>
@@ -19110,12 +18963,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Mount Salem</t>
+          <t>Vaughnsfield</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Holy Cross</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19137,7 +18990,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>holy-cross-mount-salem-st-james</t>
+          <t>st-luke-s-vaughnsfield-st-james</t>
         </is>
       </c>
     </row>
@@ -19149,12 +19002,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Vaughnsfield</t>
+          <t>Westgate</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>Holy Trinity</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19176,24 +19029,24 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>st-luke-s-vaughnsfield-st-james</t>
+          <t>holy-trinity-westgate-st-james</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>St. James</t>
+          <t>Hanover</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Westgate</t>
+          <t>Dalmally</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Holy Trinity</t>
+          <t>St. Bartholomew’s</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19215,7 +19068,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>holy-trinity-westgate-st-james</t>
+          <t>st-bartholomew-s-dalmally-hanover</t>
         </is>
       </c>
     </row>
@@ -19227,12 +19080,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Dalmally</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>St. Bartholomew’s</t>
+          <t>St. Philip’s</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -19254,7 +19107,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>st-bartholomew-s-dalmally-hanover</t>
+          <t>st-philip-s-eaton-hanover</t>
         </is>
       </c>
     </row>
@@ -19266,12 +19119,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Grange</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>St. Philip’s</t>
+          <t>St. Agnes’</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -19293,7 +19146,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>st-philip-s-eaton-hanover</t>
+          <t>st-agnes-grange-hanover</t>
         </is>
       </c>
     </row>
@@ -19305,12 +19158,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Grange</t>
+          <t>Green Island</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>St. Agnes’</t>
+          <t>Church-of-the-Holy-Trinity</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -19332,7 +19185,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>st-agnes-grange-hanover</t>
+          <t>church-of-the-holy-trinity-green-island-hanover</t>
         </is>
       </c>
     </row>
@@ -19344,12 +19197,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Green Island</t>
+          <t>Ramble</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Church-of-the-Holy-Trinity</t>
+          <t>Ramble Anglican Church</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -19359,7 +19212,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>ruin</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -19371,24 +19224,24 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>church-of-the-holy-trinity-green-island-hanover</t>
+          <t>ramble-anglican-church-hanover</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hanover</t>
+          <t>Westmoreland</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ramble</t>
+          <t>Ashton</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ramble Anglican Church</t>
+          <t>St. Alban's</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -19398,7 +19251,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ruin</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -19410,7 +19263,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ramble-anglican-church-hanover</t>
+          <t>st-alban-s-ashton-westmoreland</t>
         </is>
       </c>
     </row>
@@ -19422,12 +19275,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ashton</t>
+          <t>Beeston Spring</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>St. Alban's</t>
+          <t>St. Barnabas'</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -19449,7 +19302,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>st-alban-s-ashton-westmoreland</t>
+          <t>st-barnabas-beeston-spring-westmoreland</t>
         </is>
       </c>
     </row>
@@ -19461,12 +19314,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Beeston Spring</t>
+          <t>Berkshire</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>St. Barnabas'</t>
+          <t>St. Bartholomew's</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -19488,7 +19341,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>st-barnabas-beeston-spring-westmoreland</t>
+          <t>st-bartholomew-s-berkshire-westmoreland</t>
         </is>
       </c>
     </row>
@@ -19500,12 +19353,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Berkshire</t>
+          <t>Cessnock</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>St. Bartholomew's</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -19527,7 +19380,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>st-bartholomew-s-berkshire-westmoreland</t>
+          <t>st-luke-s-cessnock-westmoreland</t>
         </is>
       </c>
     </row>
@@ -19539,12 +19392,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cessnock</t>
+          <t>Cornwall Mountain</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>St. Stephen's</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -19566,7 +19419,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>st-luke-s-cessnock-westmoreland</t>
+          <t>st-stephen-s-cornwall-mountain-westmoreland</t>
         </is>
       </c>
     </row>
@@ -19578,12 +19431,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cornwall Mountain</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>St. Stephen's</t>
+          <t>St. Matthias</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -19605,7 +19458,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>st-stephen-s-cornwall-mountain-westmoreland</t>
+          <t>st-matthias-kentucky-westmoreland</t>
         </is>
       </c>
     </row>
@@ -19617,12 +19470,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Kings (Whitehouse)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>St. Matthias</t>
+          <t>St. Thomas'</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -19644,7 +19497,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>st-matthias-kentucky-westmoreland</t>
+          <t>st-thomas-kings-westmoreland</t>
         </is>
       </c>
     </row>
@@ -19656,12 +19509,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kings (Whitehouse)</t>
+          <t>Meylersfield</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>St. Thomas'</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -19683,7 +19536,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>st-thomas-kings-westmoreland</t>
+          <t>all-saints-meylersfield-westmoreland</t>
         </is>
       </c>
     </row>
@@ -19695,12 +19548,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Meylersfield</t>
+          <t>Mount Grace</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>Transfiguration</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -19722,7 +19575,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>all-saints-meylersfield-westmoreland</t>
+          <t>transfiguration-mount-grace-westmoreland</t>
         </is>
       </c>
     </row>
@@ -19734,12 +19587,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mount Grace</t>
+          <t>Mt. Airy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Transfiguration</t>
+          <t>St. Silas'</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -19761,24 +19614,24 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>transfiguration-mount-grace-westmoreland</t>
+          <t>st-silas-mt-airy-westmoreland</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Westmoreland</t>
+          <t>St. Elizabeth</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mt. Airy</t>
+          <t>Arlington</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>St. Silas'</t>
+          <t>St. Stephen's</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -19800,7 +19653,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>st-silas-mt-airy-westmoreland</t>
+          <t>st-stephen-s-arlington-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -19812,12 +19665,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Arlington</t>
+          <t>Bigwoods District</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>St. Stephen's</t>
+          <t>Epiphany</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19830,24 +19683,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>st-stephen-s-arlington-st-elizabeth</t>
+          <t>epiphany-bigwoods-district-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -19859,12 +19704,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bigwoods District</t>
+          <t>Burnt Savanna</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Epiphany</t>
+          <t>St. Matthew's</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19886,7 +19731,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>epiphany-bigwoods-district-st-elizabeth</t>
+          <t>st-matthew-s-burnt-savanna-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -19898,12 +19743,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bull Savannah</t>
+          <t>Middle Quarters</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>St. Aidan's</t>
+          <t>St. Margaret's</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19916,20 +19761,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>st-aidan-s-bull-savannah-st-elizabeth</t>
+          <t>st-margaret-s-middle-quarters-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -19941,12 +19782,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Burnt Savanna</t>
+          <t>Newell</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>St. Matthew's</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19956,7 +19797,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -19968,7 +19809,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>st-matthew-s-burnt-savanna-st-elizabeth</t>
+          <t>all-saints-newell-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -19980,12 +19821,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mayfield</t>
+          <t>Orange Grove</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>St. Mark's</t>
+          <t>St. Matthew's</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19998,20 +19839,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>st-mark-s-mayfield-st-elizabeth</t>
+          <t>st-matthew-s-orange-grove-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -20023,12 +19860,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Middle Quarters</t>
+          <t>Pimento Walk</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>St. Margaret's</t>
+          <t>St. Paul's Church (Old)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -20038,7 +19875,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>ruin</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -20050,7 +19887,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>st-margaret-s-middle-quarters-st-elizabeth</t>
+          <t>st-paul-s-church-old-pimento-walk-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -20062,12 +19899,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Newell</t>
+          <t>Siloah</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>St. Mark's Church</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20077,7 +19914,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -20089,7 +19926,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>all-saints-newell-st-elizabeth</t>
+          <t>st-mark-s-church-siloah-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -20101,17 +19938,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Orange Grove</t>
+          <t>Slipe</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>St. Matthew's</t>
+          <t>St. Jude's</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -20128,7 +19965,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>st-matthew-s-orange-grove-st-elizabeth</t>
+          <t>st-jude-s-slipe-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -20140,12 +19977,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pimento Walk</t>
+          <t>Stanmore Hill</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>St. Paul's Church (Old)</t>
+          <t>St Alban's</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20155,7 +19992,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ruin</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
@@ -20167,7 +20004,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>st-paul-s-church-old-pimento-walk-st-elizabeth</t>
+          <t>st-alban-s-stanmore-hill-st-elizabeth</t>
         </is>
       </c>
     </row>
@@ -20179,12 +20016,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Pondside</t>
+          <t>Tryall</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>St. Boniface</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20197,37 +20034,33 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr">
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>st-boniface-pondside-st-elizabeth</t>
+          <t>st-paul-s-tryall-st-elizabeth</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>St. Elizabeth</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Siloah</t>
+          <t>Alston</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>St. Mark's Church</t>
+          <t>St. John the Divine</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20249,29 +20082,29 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>st-mark-s-church-siloah-st-elizabeth</t>
+          <t>st-john-the-divine-alston-manchester</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>St. Elizabeth</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Slipe</t>
+          <t>Auchtembeddie</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>St. Jude's</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -20288,24 +20121,24 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>st-jude-s-slipe-st-elizabeth</t>
+          <t>st-john-s-auchtembeddie-manchester</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>St. Elizabeth</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Southfield</t>
+          <t>Battersea</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>St. Mary's</t>
+          <t>St. Jude's</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20318,37 +20151,33 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>st-mary-s-southfield-st-elizabeth</t>
+          <t>st-jude-s-battersea-manchester</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>St. Elizabeth</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Stanmore Hill</t>
+          <t>Comfort Hall</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>St Alban's</t>
+          <t>St. Simon's</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -20370,24 +20199,24 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>st-alban-s-stanmore-hill-st-elizabeth</t>
+          <t>st-simon-s-comfort-hall-manchester</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>St. Elizabeth</t>
+          <t>Manchester</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tryall</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. Lawrence's</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -20400,24 +20229,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H129" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>st-paul-s-tryall-st-elizabeth</t>
+          <t>st-lawrence-s-devon-manchester</t>
         </is>
       </c>
     </row>
@@ -20429,12 +20250,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Alston</t>
+          <t>Georges Valley</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>St. John the Divine</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -20447,24 +20268,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H130" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>st-john-the-divine-alston-manchester</t>
+          <t>st-george-s-georges-valley-manchester</t>
         </is>
       </c>
     </row>
@@ -20476,12 +20289,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Auchtembeddie</t>
+          <t>Harmons</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>St. Andrew's</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -20503,7 +20316,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>st-john-s-auchtembeddie-manchester</t>
+          <t>st-andrew-s-harmons-manchester</t>
         </is>
       </c>
     </row>
@@ -20515,12 +20328,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Battersea</t>
+          <t>Harry Watch</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>St. Jude's</t>
+          <t>Harry Watch</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -20533,24 +20346,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H132" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>st-jude-s-battersea-manchester</t>
+          <t>harry-watch-manchester</t>
         </is>
       </c>
     </row>
@@ -20562,12 +20367,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Comfort Hall</t>
+          <t>Kendal</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>St. Simon's</t>
+          <t>St. James'</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -20589,7 +20394,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>st-simon-s-comfort-hall-manchester</t>
+          <t>st-james-kendal-manchester</t>
         </is>
       </c>
     </row>
@@ -20601,12 +20406,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Mile Gully</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>St. Lawrence's</t>
+          <t>St. Barnabas'</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -20628,7 +20433,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>st-lawrence-s-devon-manchester</t>
+          <t>st-barnabas-mile-gully-manchester</t>
         </is>
       </c>
     </row>
@@ -20640,12 +20445,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Georges Valley</t>
+          <t>Mile Gully</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>St. Paul's Church</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -20658,24 +20463,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F135" s="5" t="inlineStr">
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H135" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>st-george-s-georges-valley-manchester</t>
+          <t>st-paul-s-church-mile-gully-manchester</t>
         </is>
       </c>
     </row>
@@ -20687,12 +20484,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Harmons</t>
+          <t>New Forest</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>St. Andrew's</t>
+          <t>St. Michael and All Angels</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -20705,24 +20502,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H136" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>st-andrew-s-harmons-manchester</t>
+          <t>st-michael-and-all-angels-manchester</t>
         </is>
       </c>
     </row>
@@ -20734,12 +20523,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Harry Watch</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Harry Watch</t>
+          <t>St. Patrick's</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -20752,24 +20541,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F137" s="5" t="inlineStr">
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H137" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>harry-watch-manchester</t>
+          <t>st-patrick-s-providence-manchester</t>
         </is>
       </c>
     </row>
@@ -20781,17 +20562,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kendal</t>
+          <t>Spalding</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>St. James'</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -20808,7 +20589,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>st-james-kendal-manchester</t>
+          <t>st-paul-s-spalding-manchester</t>
         </is>
       </c>
     </row>
@@ -20820,12 +20601,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Mile Gully</t>
+          <t>St. Toolies</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>St. Barnabas'</t>
+          <t>Holy Trinity</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -20847,7 +20628,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>st-barnabas-mile-gully-manchester</t>
+          <t>holy-trinity-st-toolies-manchester</t>
         </is>
       </c>
     </row>
@@ -20859,12 +20640,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mile Gully</t>
+          <t>Whitby</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>St. Paul's Church</t>
+          <t>St. Peter's</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20886,7 +20667,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>st-paul-s-church-mile-gully-manchester</t>
+          <t>whitby-manchester</t>
         </is>
       </c>
     </row>
@@ -20898,12 +20679,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>New Forest</t>
+          <t>Williamsfield</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>St. Michael and All Angels</t>
+          <t>St. Mark's Church</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20916,41 +20697,33 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr">
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H141" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>st-michael-and-all-angels-manchester</t>
+          <t>st-mark-s-church-williamsfield-manchester</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Clarendon</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Beckford Kraal</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>St. Patrick's</t>
+          <t>St. Mark's</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20972,29 +20745,29 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>st-patrick-s-providence-manchester</t>
+          <t>st-mark-s-beckford-kraal-clarendon</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Clarendon</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Spalding</t>
+          <t>Frankfield</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. Bartholomew's</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -21011,24 +20784,24 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>st-paul-s-spalding-manchester</t>
+          <t>st-bartholomew-s-frankfield-clarendon</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Clarendon</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>St. Toolies</t>
+          <t>Good Hope</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Holy Trinity</t>
+          <t>St. Bartholomew's</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -21038,44 +20811,36 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr">
+          <t>inactive</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H144" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>holy-trinity-st-toolies-manchester</t>
+          <t>st-bartholomew-s-good-hope-clarendon</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Clarendon</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Whitby</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>St. Peter's</t>
+          <t>St. James'</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -21088,41 +20853,33 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F145" s="5" t="inlineStr">
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H145" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>whitby-manchester</t>
+          <t>st-james-hayes-clarendon</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Clarendon</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Williamsfield</t>
+          <t>Mitchell Town</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>St. Mark's Church</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -21144,7 +20901,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>st-mark-s-church-williamsfield-manchester</t>
+          <t>st-luke-s-mitchell-town-clarendon</t>
         </is>
       </c>
     </row>
@@ -21156,12 +20913,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Arthur's Seat</t>
+          <t>Mt. Providence</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>St. Michael's</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21174,20 +20931,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr">
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G147" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>st-michael-s-arthurs-seat-clarendon</t>
+          <t>all-saints-mt-providence-clarendon</t>
         </is>
       </c>
     </row>
@@ -21199,12 +20952,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Beckford Kraal</t>
+          <t>Palmers Cross</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>St. Mark's</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -21226,7 +20979,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>st-mark-s-beckford-kraal-clarendon</t>
+          <t>st-john-s-palmers-cross-clarendon</t>
         </is>
       </c>
     </row>
@@ -21238,12 +20991,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Frankfield</t>
+          <t>Park Hall</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>St. Bartholomew's</t>
+          <t>Holy Trinity</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -21265,7 +21018,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>st-bartholomew-s-frankfield-clarendon</t>
+          <t>holy-trinity-park-hall-clarendon</t>
         </is>
       </c>
     </row>
@@ -21277,12 +21030,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Good Hope</t>
+          <t>Peckham</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>St. Bartholomew's</t>
+          <t>Peckham</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21292,7 +21045,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
@@ -21304,7 +21057,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>st-bartholomew-s-good-hope-clarendon</t>
+          <t>peckham-clarendon</t>
         </is>
       </c>
     </row>
@@ -21316,12 +21069,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Portland Cottage</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>St. James'</t>
+          <t>St. John's</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21331,7 +21084,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -21343,7 +21096,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>st-james-hayes-clarendon</t>
+          <t>st-john-s-portland-cottage-clarendon</t>
         </is>
       </c>
     </row>
@@ -21355,12 +21108,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Mitchell Town</t>
+          <t>Race Course</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>St. Thomas'</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21373,24 +21126,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F152" s="5" t="inlineStr">
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H152" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>st-luke-s-mitchell-town-clarendon</t>
+          <t>st-thomas-race-course-clarendon</t>
         </is>
       </c>
     </row>
@@ -21402,12 +21147,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Mt. Providence</t>
+          <t>Red Hills (Clarendon)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21420,24 +21165,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F153" s="5" t="inlineStr">
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H153" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>all-saints-mt-providence-clarendon</t>
+          <t>st-george-s-red-hills-clarendon</t>
         </is>
       </c>
     </row>
@@ -21449,12 +21186,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Palmers Cross</t>
+          <t>Rhoden Hall</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>St. Peter's</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -21476,7 +21213,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>st-john-s-palmers-cross-clarendon</t>
+          <t>st-peter-s-rhoden-hall-clarendon</t>
         </is>
       </c>
     </row>
@@ -21488,12 +21225,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Park Hall</t>
+          <t>Richmond Park</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Holy Trinity</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -21515,7 +21252,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>holy-trinity-park-hall-clarendon</t>
+          <t>all-saints-richmond-park-clarendon</t>
         </is>
       </c>
     </row>
@@ -21527,12 +21264,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Peckham</t>
+          <t>Rock River</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Peckham</t>
+          <t>St. James'</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -21545,24 +21282,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F156" s="5" t="inlineStr">
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G156" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H156" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>peckham-clarendon</t>
+          <t>st-james-rock-river-clarendon</t>
         </is>
       </c>
     </row>
@@ -21574,12 +21303,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Porous</t>
+          <t>Rocky Point</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>St. Augustine's Church</t>
+          <t>St. Andrew's</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -21601,7 +21330,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>st-augustine-s-church-porous-clarendon</t>
+          <t>st-andrew-s-rocky-point-clarendon</t>
         </is>
       </c>
     </row>
@@ -21613,12 +21342,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Portland Cottage</t>
+          <t>Sanguinetti</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>St. John's</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -21628,7 +21357,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
@@ -21640,7 +21369,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>st-john-s-portland-cottage-clarendon</t>
+          <t>st-luke-s-sanguinetti-clarendon</t>
         </is>
       </c>
     </row>
@@ -21652,22 +21381,22 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Race Course</t>
+          <t>The Cross</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>St. Thomas'</t>
+          <t>Church of the White Cross (Ruins)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>ruin</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>ruin</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
@@ -21679,7 +21408,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>st-thomas-race-course-clarendon</t>
+          <t>church-of-the-white-cross-ruins-the-cross-clarendon</t>
         </is>
       </c>
     </row>
@@ -21691,12 +21420,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Red Hills (Clarendon)</t>
+          <t>Toll Gate</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>St. James'</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21718,7 +21447,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>st-george-s-red-hills-clarendon</t>
+          <t>st-james-s-toll-gate-clarendon</t>
         </is>
       </c>
     </row>
@@ -21730,17 +21459,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Rhoden Hall</t>
+          <t>Wood Hall</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>St. Peter's</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>chapel</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -21757,24 +21486,24 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>st-peter-s-rhoden-hall-clarendon</t>
+          <t>st-luke-s-wood-hall-clarendon</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Clarendon</t>
+          <t>St. Catherine</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Richmond Park</t>
+          <t>Bartons</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21796,24 +21525,24 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>all-saints-richmond-park-clarendon</t>
+          <t>st-george-s-bartons-st-catherine</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Clarendon</t>
+          <t>St. Catherine</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Rock River</t>
+          <t>Blackstonedge</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>St. James'</t>
+          <t>St. George's</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21823,7 +21552,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
@@ -21835,24 +21564,24 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>st-james-rock-river-clarendon</t>
+          <t>st-george-s-blackstonedge-st-catherine</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Clarendon</t>
+          <t>St. Catherine</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Rocky Point</t>
+          <t>Camperdown</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>St. Andrew's</t>
+          <t>St. Lawrence's</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21865,41 +21594,33 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F164" s="5" t="inlineStr">
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G164" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H164" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>st-andrew-s-rocky-point-clarendon</t>
+          <t>st-lawrence-s-camperdown-st-catherine</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Clarendon</t>
+          <t>St. Catherine</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sanguinetti</t>
+          <t>Clapham</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21921,34 +21642,34 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>st-luke-s-sanguinetti-clarendon</t>
+          <t>st-paul-s-clapham-st-catherine</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Clarendon</t>
+          <t>St. Catherine</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>The Cross</t>
+          <t>Crescent</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Church of the White Cross (Ruins)</t>
+          <t>St. Barnabas'</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ruin</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ruin</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
@@ -21960,24 +21681,24 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>church-of-the-white-cross-ruins-the-cross-clarendon</t>
+          <t>st-barnabas-crescent-st-catherine</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Clarendon</t>
+          <t>St. Catherine</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Toll Gate</t>
+          <t>Faith's</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>St. James'</t>
+          <t>St. Faith's</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21990,46 +21711,38 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F167" s="5" t="inlineStr">
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G167" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H167" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>st-james-s-toll-gate-clarendon</t>
+          <t>st-faith-s-faith-s-st-catherine</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Clarendon</t>
+          <t>St. Catherine</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Wood Hall</t>
+          <t>Freetown</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>SS Michael and George's</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>chapel</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -22037,24 +21750,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F168" s="5" t="inlineStr">
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H168" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>st-luke-s-wood-hall-clarendon</t>
+          <t>ss-michael-and-george-s-freetown-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22066,22 +21771,22 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Bartons</t>
+          <t>Goffe / Goba (district)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>mission</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -22093,7 +21798,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>st-george-s-bartons-st-catherine</t>
+          <t>st-paul-s-goba-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22105,12 +21810,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Blackstonedge</t>
+          <t>Guy's Hill</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>St. George's</t>
+          <t>All Saints'</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22120,7 +21825,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -22132,7 +21837,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>st-george-s-blackstonedge-st-catherine</t>
+          <t>all-saints-guys-hill-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22144,12 +21849,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Camperdown</t>
+          <t>Ham Walk</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>St. Lawrence's</t>
+          <t>St. Mark's</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22162,24 +21867,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F171" s="5" t="inlineStr">
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G171" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>st-lawrence-s-camperdown-st-catherine</t>
+          <t>st-mark-s-ham-walk-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22191,12 +21888,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Clapham</t>
+          <t>Harewood</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. Saviour's</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22209,24 +21906,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F172" s="5" t="inlineStr">
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G172" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H172" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>st-paul-s-clapham-st-catherine</t>
+          <t>st-saviour-s-harewood-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22238,12 +21927,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Crescent</t>
+          <t>Innswood/McCook's Pen</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>St. Barnabas'</t>
+          <t>St. Joseph's</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22265,7 +21954,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>st-barnabas-crescent-st-catherine</t>
+          <t>st-joseph-s-innswood-mccook-s-pen-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22277,12 +21966,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Faith's</t>
+          <t>Juan-de-Bolas</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>St. Faith's</t>
+          <t>St. Luke's</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22304,7 +21993,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>st-faith-s-faith-s-st-catherine</t>
+          <t>st-luke-s-juan-de-bolas-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22316,12 +22005,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Freetown</t>
+          <t>Kentish</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SS Michael and George's</t>
+          <t>St. Paul's</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22334,24 +22023,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F175" s="5" t="inlineStr">
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G175" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H175" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>ss-michael-and-george-s-freetown-st-catherine</t>
+          <t>st-paul-s-kentish-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22363,22 +22044,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Goffe / Goba (district)</t>
+          <t>Linstead</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>St. John's Church</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>mission</t>
+          <t>church</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
@@ -22390,7 +22071,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>st-paul-s-goba-st-catherine</t>
+          <t>st-john-s-church-linstead-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22402,12 +22083,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Guy's Hill</t>
+          <t>Macca Tree</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>All Saints'</t>
+          <t>St. Mark's</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -22420,24 +22101,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F177" s="5" t="inlineStr">
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G177" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H177" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>all-saints-guys-hill-st-catherine</t>
+          <t>st-mark-s-macca-tree-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22449,12 +22122,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ham Walk</t>
+          <t>Mount Industry</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>St. Mark's</t>
+          <t>St. Boniface</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -22476,7 +22149,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>st-mark-s-ham-walk-st-catherine</t>
+          <t>st-boniface-mount-industry-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22488,12 +22161,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Harewood</t>
+          <t>Mount Moreland</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>St. Saviour's</t>
+          <t>St. Matthew's</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -22515,7 +22188,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>st-saviour-s-harewood-st-catherine</t>
+          <t>st-matthew-s-mt-moorland-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22527,12 +22200,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Innswood/McCook's Pen</t>
+          <t>Old Harbour</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>St. Joseph's</t>
+          <t>Holy Trinity</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -22542,7 +22215,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -22554,7 +22227,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>st-joseph-s-innswood-mccook-s-pen-st-catherine</t>
+          <t>holy-trinity-old-harbour-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22566,12 +22239,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Juan-de-Bolas</t>
+          <t>Old Works</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>St. Luke's</t>
+          <t>St. Peter's</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -22584,24 +22257,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F181" s="5" t="inlineStr">
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G181" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H181" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>st-luke-s-juan-de-bolas-st-catherine</t>
+          <t>st-peter-s-old-works-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22613,12 +22278,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Kentish</t>
+          <t>Portmore</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>St. Paul's</t>
+          <t>Church of Reconciliation</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22631,24 +22296,16 @@
           <t>active</t>
         </is>
       </c>
-      <c r="F182" s="5" t="inlineStr">
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" s="5" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="G182" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H182" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>st-paul-s-kentish-st-catherine</t>
+          <t>church-of-reconciliation-portmore-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22660,12 +22317,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Linstead</t>
+          <t>Spanish Town</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>St. John's Church</t>
+          <t>Holy Trinity</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22675,7 +22332,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -22687,7 +22344,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>st-john-s-church-linstead-st-catherine</t>
+          <t>holy-trinity-spanish-town-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22699,12 +22356,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Macca Tree</t>
+          <t>Top Hill</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>St. Mark's</t>
+          <t>St. Simon's</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22726,7 +22383,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>st-mark-s-macca-tree-st-catherine</t>
+          <t>st-simon-s-top-hill-st-catherine</t>
         </is>
       </c>
     </row>
@@ -22738,12 +22395,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mount Industry</t>
+          <t>Watermount</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>St. Boniface</t>
+          <t>St. Augustine's</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22765,301 +22422,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>st-boniface-mount-industry-st-catherine</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>St. Catherine</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Mount Moreland</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>St. Matthew's</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>st-matthew-s-mt-moorland-st-catherine</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>St. Catherine</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Old Harbour</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Holy Trinity</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>holy-trinity-old-harbour-st-catherine</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>St. Catherine</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Old Works</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>St. Peter's</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>st-peter-s-old-works-st-catherine</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>St. Catherine</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Portmore</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Church of Reconciliation</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H189" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>church-of-reconciliation-portmore-st-catherine</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>St. Catherine</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Spanish Town</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Holy Trinity</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>holy-trinity-spanish-town-st-catherine</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>St. Catherine</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Top Hill</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>St. Simon's</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F191" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="G191" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="H191" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>st-simon-s-top-hill-st-catherine</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>St. Catherine</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Watermount</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>St. Augustine's</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" s="5" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
           <t>st-augustine-s-watermount-st-catherine</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I192"/>
+  <autoFilter ref="A1:I185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>